--- a/admission_checklist_forms/008_medical_school_admission_checklist_form_template--admission_checklist_forms.xlsx
+++ b/admission_checklist_forms/008_medical_school_admission_checklist_form_template--admission_checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_''}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': ''}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'under_review'}</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Under Review'}</t>
+          <t>Under Review</t>
         </is>
       </c>
     </row>
@@ -998,29 +998,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>application_status_choices</t>
+          <t>medical_school_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_4'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 4'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_5'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 5'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_6'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Option 6'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_7'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 7'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_8'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 8'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option_9'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Option 9'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option_10'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Option 10'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_11'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 11'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_12'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 12'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option_13'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Option 13'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option_14'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Option 14'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option_15'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Option 15'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option_16'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Option 16'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'option_17'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Option 17'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'option_18'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Option 18'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'option_19'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Option 19'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option_20'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Option 20'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'option_21'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Option 21'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'option_22'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Option 22'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'option_23'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Option 23'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>medical_school_choices</t>
+          <t>application_process_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'option_24'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Option 24'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1457,29 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>application_process_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
